--- a/Assets/Config/Excel/Item.xlsx
+++ b/Assets/Config/Excel/Item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,100 @@
       </c>
       <c r="M6" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>金币</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>item_coin</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>游戏货币，用于购买商品</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>货币</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>icon_coin</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>钻石</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>item_diamond</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>稀有货币，用于购买商品</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>货币</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>icon_diamond</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
